--- a/artfynd/A 6614-2026 artfynd.xlsx
+++ b/artfynd/A 6614-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111113072</v>
+        <v>119839406</v>
       </c>
       <c r="B2" t="n">
-        <v>78081</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örasjöberget_Norr, Hls</t>
+          <t>Örasjön, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505703.418272233</v>
+        <v>505788</v>
       </c>
       <c r="R2" t="n">
-        <v>6896431.164464442</v>
+        <v>6896077</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,15 +760,850 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>111109176</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Örasjöberget norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>505602</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6896735</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111109182</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Örasjöberget norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>505602</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6896735</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>111109523</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Örasjöberget N, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>505593</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6896685</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isaac Tiselius</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isaac Tiselius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111111030</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Örasjöberget N, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>505774</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6896714</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Susanna Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Susanna Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111110787</v>
+      </c>
+      <c r="B7" t="n">
+        <v>41601</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>215713</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grå blåbärsfältmätare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Entephria caesiata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Örasjöberget Norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>505579</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6896685</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111109191</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Örasjöberget norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>505605</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6896722</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111109512</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Örasjöberget N, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>505592</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6896686</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isaac Tiselius</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isaac Tiselius</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111113072</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Örasjöberget_Norr, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>505703</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6896431</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Evalena Sköld</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>

--- a/artfynd/A 6614-2026 artfynd.xlsx
+++ b/artfynd/A 6614-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119839406</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109176</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109182</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109523</t>
         </is>
       </c>
     </row>
@@ -1190,6 +1215,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111111030</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110787</t>
         </is>
       </c>
     </row>
@@ -1406,6 +1441,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109191</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,6 +1547,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109512</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1608,8 +1653,24 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111113072</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>